--- a/data/trans_orig/P1401-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1401-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cáncer en 2012</t>
+          <t>Población con diagnóstico de cáncer en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10546</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28448</t>
+          <t>27906</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27204</t>
+          <t>27033</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52383</t>
+          <t>53130</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41627</t>
+          <t>41985</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72293</t>
+          <t>74246</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,21%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>946195</t>
+          <t>946737</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>964097</t>
+          <t>964337</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,94%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1285414</t>
+          <t>1284667</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1310593</t>
+          <t>1310764</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2240147</t>
+          <t>2238194</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2270813</t>
+          <t>2270455</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>96,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,18%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12239</t>
+          <t>11949</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30642</t>
+          <t>30610</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18776</t>
+          <t>19055</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>42569</t>
+          <t>43291</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>35462</t>
+          <t>34617</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>66404</t>
+          <t>65359</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1933315</t>
+          <t>1933347</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1951718</t>
+          <t>1952008</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1712023</t>
+          <t>1711301</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1735816</t>
+          <t>1735537</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3652145</t>
+          <t>3653190</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3683087</t>
+          <t>3683932</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,07%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>7420</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1057</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10682</t>
+          <t>10750</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2226</t>
+          <t>2342</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13497</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>474624</t>
+          <t>473761</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>447949</t>
+          <t>447881</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457580</t>
+          <t>457574</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>926316</t>
+          <t>926411</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>937587</t>
+          <t>937471</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27382</t>
+          <t>26976</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54406</t>
+          <t>54219</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55299</t>
+          <t>55179</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90759</t>
+          <t>89869</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>90381</t>
+          <t>91672</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>132919</t>
+          <t>134614</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3365376</t>
+          <t>3365563</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3392400</t>
+          <t>3392806</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,21%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3460261</t>
+          <t>3461151</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3495721</t>
+          <t>3495841</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6837882</t>
+          <t>6836187</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6880420</t>
+          <t>6879129</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cáncer en 2016</t>
+          <t>Población con diagnóstico de cáncer en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8050</t>
+          <t>8106</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23176</t>
+          <t>22421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2355,7 +2355,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18490</t>
+          <t>17850</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43497</t>
+          <t>41633</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29953</t>
+          <t>29836</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57725</t>
+          <t>56350</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,22%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>731171</t>
+          <t>731926</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>746297</t>
+          <t>746241</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,7 +2463,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>951163</t>
+          <t>953027</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>976170</t>
+          <t>976810</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1691282</t>
+          <t>1692657</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1719054</t>
+          <t>1719171</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7417</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22166</t>
+          <t>22186</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>16217</t>
+          <t>17346</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38783</t>
+          <t>37790</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28462</t>
+          <t>26758</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54750</t>
+          <t>52833</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,3%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2054219</t>
+          <t>2054199</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2068968</t>
+          <t>2069076</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,64%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1949517</t>
+          <t>1950510</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1972083</t>
+          <t>1970954</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4009935</t>
+          <t>4011852</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4036223</t>
+          <t>4037927</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,34%</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>7415</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10749</t>
+          <t>10959</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28011</t>
+          <t>28974</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12723</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>31424</t>
+          <t>30833</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>538890</t>
+          <t>539471</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>521129</t>
+          <t>520166</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>538391</t>
+          <t>538181</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1064603</t>
+          <t>1065194</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1083304</t>
+          <t>1084038</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,19%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20404</t>
+          <t>20897</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42284</t>
+          <t>42442</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>52921</t>
+          <t>54630</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>88586</t>
+          <t>90563</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83293</t>
+          <t>84047</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123185</t>
+          <t>122599</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,77%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3335334</t>
+          <t>3335176</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3357214</t>
+          <t>3356721</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,4%</t>
+          <t>99,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3443514</t>
+          <t>3441537</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3479179</t>
+          <t>3477470</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6786533</t>
+          <t>6787119</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6826425</t>
+          <t>6825671</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,78%</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de cáncer en 2023</t>
+          <t>Población con diagnóstico de cáncer en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3938,12 +3938,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10571</t>
+          <t>10416</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23127</t>
+          <t>23374</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25354</t>
+          <t>25396</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40268</t>
+          <t>40911</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>39151</t>
+          <t>38837</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59187</t>
+          <t>59192</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489330</t>
+          <t>489083</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>501886</t>
+          <t>502041</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>711672</t>
+          <t>711029</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>726586</t>
+          <t>726544</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1205211</t>
+          <t>1205206</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1225247</t>
+          <t>1225561</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>96,93%</t>
         </is>
       </c>
     </row>
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>24034</t>
+          <t>25033</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49094</t>
+          <t>51025</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4316,12 +4316,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25210</t>
+          <t>25676</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47151</t>
+          <t>47115</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56154</t>
+          <t>56386</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>89231</t>
+          <t>90836</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2238416</t>
+          <t>2236485</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2263476</t>
+          <t>2262477</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2187488</t>
+          <t>2187524</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2209429</t>
+          <t>2208963</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4432917</t>
+          <t>4431312</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4465994</t>
+          <t>4465762</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,75%</t>
         </is>
       </c>
     </row>
@@ -4624,12 +4624,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10511</t>
+          <t>9942</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24801</t>
+          <t>24288</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4639,12 +4639,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4659,12 +4659,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5650</t>
+          <t>5640</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15501</t>
+          <t>15391</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4674,12 +4674,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17842</t>
+          <t>17830</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35740</t>
+          <t>35580</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -4737,12 +4737,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>620762</t>
+          <t>621275</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>635052</t>
+          <t>635621</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4772,12 +4772,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>644962</t>
+          <t>645072</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>654813</t>
+          <t>654823</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4787,12 +4787,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1270286</t>
+          <t>1270446</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1288184</t>
+          <t>1288196</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50660</t>
+          <t>52018</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86561</t>
+          <t>84801</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62236</t>
+          <t>62045</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>94755</t>
+          <t>92996</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123337</t>
+          <t>125037</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>169826</t>
+          <t>173663</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,45%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3358969</t>
+          <t>3360729</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3394870</t>
+          <t>3393512</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,12 +5095,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3552287</t>
+          <t>3554046</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3584806</t>
+          <t>3584997</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,12 +5130,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6922746</t>
+          <t>6918909</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6969235</t>
+          <t>6967535</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,24%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1401-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1401-Estudios-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27906</t>
+          <t>28213</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27033</t>
+          <t>26097</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53130</t>
+          <t>51119</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41985</t>
+          <t>42303</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>74246</t>
+          <t>74269</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,7 +817,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>946737</t>
+          <t>946430</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>964337</t>
+          <t>965047</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1284667</t>
+          <t>1286678</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1310764</t>
+          <t>1311700</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2238194</t>
+          <t>2238171</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2270455</t>
+          <t>2270137</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>98,17%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11949</t>
+          <t>12516</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>30610</t>
+          <t>31046</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19055</t>
+          <t>19973</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>43291</t>
+          <t>43123</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>34617</t>
+          <t>34184</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>65359</t>
+          <t>64189</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1933347</t>
+          <t>1932911</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1952008</t>
+          <t>1951441</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,44%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1711301</t>
+          <t>1711469</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1735537</t>
+          <t>1734619</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,53%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3653190</t>
+          <t>3654360</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3683932</t>
+          <t>3684365</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7420</t>
+          <t>7424</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1057</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>10597</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2342</t>
+          <t>2983</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>13402</t>
+          <t>14032</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>473761</t>
+          <t>473757</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>447881</t>
+          <t>448034</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>457574</t>
+          <t>457585</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>926411</t>
+          <t>925781</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>937471</t>
+          <t>936830</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>26976</t>
+          <t>27595</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54219</t>
+          <t>53446</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55179</t>
+          <t>54431</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89869</t>
+          <t>90370</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>91672</t>
+          <t>92212</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>134614</t>
+          <t>134728</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3365563</t>
+          <t>3366336</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3392806</t>
+          <t>3392187</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3461151</t>
+          <t>3460650</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3495841</t>
+          <t>3496589</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6836187</t>
+          <t>6836073</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6879129</t>
+          <t>6878589</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>8106</t>
+          <t>7755</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>22421</t>
+          <t>22196</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2350,12 +2350,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17850</t>
+          <t>19560</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41633</t>
+          <t>42742</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2385,12 +2385,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29836</t>
+          <t>29664</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56350</t>
+          <t>57329</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,28%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>731926</t>
+          <t>732151</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>746241</t>
+          <t>746592</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>953027</t>
+          <t>951918</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>976810</t>
+          <t>975100</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1692657</t>
+          <t>1691678</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1719171</t>
+          <t>1719343</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,3%</t>
         </is>
       </c>
     </row>
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7309</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22186</t>
+          <t>22382</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17346</t>
+          <t>16995</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37790</t>
+          <t>38792</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2728,12 +2728,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>26758</t>
+          <t>27910</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52833</t>
+          <t>54391</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2054199</t>
+          <t>2054003</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2069076</t>
+          <t>2069063</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1950510</t>
+          <t>1949508</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1970954</t>
+          <t>1971305</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4011852</t>
+          <t>4010294</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4037927</t>
+          <t>4036775</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -3021,12 +3021,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>735</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7415</t>
+          <t>7737</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10959</t>
+          <t>10891</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28974</t>
+          <t>29046</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3071,12 +3071,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>11989</t>
+          <t>12857</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>30833</t>
+          <t>30063</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3106,12 +3106,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,74%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>539471</t>
+          <t>539149</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>546152</t>
+          <t>546151</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,64%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>520166</t>
+          <t>520094</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>538181</t>
+          <t>538249</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1065194</t>
+          <t>1065964</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1084038</t>
+          <t>1083170</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20897</t>
+          <t>21179</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42442</t>
+          <t>43194</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54630</t>
+          <t>55649</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90563</t>
+          <t>92782</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84047</t>
+          <t>80741</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>122599</t>
+          <t>123218</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3335176</t>
+          <t>3334424</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3356721</t>
+          <t>3356439</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3441537</t>
+          <t>3439318</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3477470</t>
+          <t>3476451</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6787119</t>
+          <t>6786500</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6825671</t>
+          <t>6828977</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -3933,32 +3933,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>16060</t>
+          <t>16899</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>10696</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>23374</t>
+          <t>24309</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3968,17 +3968,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>32407</t>
+          <t>35348</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25396</t>
+          <t>27598</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40911</t>
+          <t>44434</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4003,32 +4003,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>48467</t>
+          <t>52247</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>38837</t>
+          <t>42971</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59192</t>
+          <t>63836</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,57%</t>
         </is>
       </c>
     </row>
@@ -4046,32 +4046,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>496397</t>
+          <t>559034</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>489083</t>
+          <t>551624</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>502041</t>
+          <t>565237</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,87%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,78%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4081,17 +4081,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>719533</t>
+          <t>784534</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>711029</t>
+          <t>775448</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>726544</t>
+          <t>792284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,56%</t>
+          <t>94,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4116,32 +4116,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1215931</t>
+          <t>1343568</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1205206</t>
+          <t>1331979</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1225561</t>
+          <t>1352844</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>96,26%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -4159,17 +4159,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>512457</t>
+          <t>575933</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>512457</t>
+          <t>575933</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>512457</t>
+          <t>575933</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4194,17 +4194,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>751940</t>
+          <t>819882</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>751940</t>
+          <t>819882</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>751940</t>
+          <t>819882</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4229,17 +4229,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1264398</t>
+          <t>1395815</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1264398</t>
+          <t>1395815</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1264398</t>
+          <t>1395815</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36733</t>
+          <t>39007</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25033</t>
+          <t>28482</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51025</t>
+          <t>52552</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>36133</t>
+          <t>38821</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>25676</t>
+          <t>30185</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47115</t>
+          <t>49765</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4346,32 +4346,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>72866</t>
+          <t>77828</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>56386</t>
+          <t>64584</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>90836</t>
+          <t>94120</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,14%</t>
         </is>
       </c>
     </row>
@@ -4389,32 +4389,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2250777</t>
+          <t>2187531</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2236485</t>
+          <t>2173986</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2262477</t>
+          <t>2198056</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4424,32 +4424,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2198506</t>
+          <t>2128764</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2187524</t>
+          <t>2117820</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2208963</t>
+          <t>2137400</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,38%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,85%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4459,32 +4459,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>4449282</t>
+          <t>4316294</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4431312</t>
+          <t>4300002</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4465762</t>
+          <t>4329538</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,53%</t>
         </is>
       </c>
     </row>
@@ -4502,17 +4502,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2287510</t>
+          <t>2226538</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2287510</t>
+          <t>2226538</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2287510</t>
+          <t>2226538</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4537,17 +4537,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2234639</t>
+          <t>2167585</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2234639</t>
+          <t>2167585</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2234639</t>
+          <t>2167585</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4572,17 +4572,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4522148</t>
+          <t>4394122</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4522148</t>
+          <t>4394122</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4522148</t>
+          <t>4394122</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4619,32 +4619,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16084</t>
+          <t>18601</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9942</t>
+          <t>12376</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24288</t>
+          <t>28752</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4654,32 +4654,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>9400</t>
+          <t>10649</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5640</t>
+          <t>5970</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15391</t>
+          <t>16482</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4689,32 +4689,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>25484</t>
+          <t>29250</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>17830</t>
+          <t>20695</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35580</t>
+          <t>40033</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,77%</t>
         </is>
       </c>
     </row>
@@ -4732,32 +4732,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>629479</t>
+          <t>691854</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>621275</t>
+          <t>681703</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>635621</t>
+          <t>698079</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,51%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4767,32 +4767,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>651063</t>
+          <t>724228</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>645072</t>
+          <t>718395</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>654823</t>
+          <t>728907</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,15%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4802,32 +4802,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1280542</t>
+          <t>1416082</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1270446</t>
+          <t>1405299</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1288196</t>
+          <t>1424637</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,57%</t>
         </is>
       </c>
     </row>
@@ -4845,17 +4845,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>645563</t>
+          <t>710455</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>645563</t>
+          <t>710455</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>645563</t>
+          <t>710455</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4880,17 +4880,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>660463</t>
+          <t>734877</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4915,17 +4915,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1306026</t>
+          <t>1445332</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1306026</t>
+          <t>1445332</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1306026</t>
+          <t>1445332</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4962,32 +4962,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>68877</t>
+          <t>74507</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52018</t>
+          <t>61422</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84801</t>
+          <t>91712</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4997,32 +4997,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>77940</t>
+          <t>84818</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>62045</t>
+          <t>71320</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>92996</t>
+          <t>98026</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5032,32 +5032,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>146817</t>
+          <t>159325</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>125037</t>
+          <t>139789</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>173663</t>
+          <t>181133</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -5075,32 +5075,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>3376653</t>
+          <t>3438418</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3360729</t>
+          <t>3421213</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3393512</t>
+          <t>3451503</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5110,32 +5110,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3569102</t>
+          <t>3637526</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3554046</t>
+          <t>3624318</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3584997</t>
+          <t>3651024</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>6945755</t>
+          <t>7075944</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6918909</t>
+          <t>7054136</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6967535</t>
+          <t>7095480</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,07%</t>
         </is>
       </c>
     </row>
@@ -5188,17 +5188,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3445530</t>
+          <t>3512925</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3445530</t>
+          <t>3512925</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3445530</t>
+          <t>3512925</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3647042</t>
+          <t>3722344</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3647042</t>
+          <t>3722344</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3647042</t>
+          <t>3722344</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5258,17 +5258,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>7092572</t>
+          <t>7235269</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>7092572</t>
+          <t>7235269</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>7092572</t>
+          <t>7235269</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
